--- a/Hoadon/HD2026/HDVao/6/3502550210_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HD2026/HDVao/6/3502550210_HDDienTuDaCapMa.xlsx
@@ -314,6 +314,5310 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C26TBR</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>24424</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>0100520429-001</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH DỊCH VỤ VÀ THƯƠNG MẠI MESA</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>1647740.0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>131819.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>1779559.0</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C26TAA</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>2828</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>1101929209</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI XUẤT NHẬP KHẨU CHẾ BIẾN THỰC PHẨM TẤN TẤN PHÚC</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>1.1574074E7</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>1.25E7</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C26TTD</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>13450</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3500370861</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>DOANH NGHIỆP TƯ NHÂN TIẾN ĐẠT</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>2.988285E8</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>2.988285E7</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>3.2871135E8</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C26THT</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>13512</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3500405761</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>5727273.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>572727.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>6300000.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C26THT</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>13513</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3500405761</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>3866666.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>309334.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>4176000.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C26THT</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>13644</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3500405761</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>2919252.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>233540.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>3152792.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C26TOA</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3500405761</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>6643476.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>531478.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>7174954.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C26TOA</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3500405761</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>4910186.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>392814.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
+        <v>5303000.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C26TOA</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3500405761</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>1061112.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>84888.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>1146000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C26TOA</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>1621</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3500405761</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HỒNG THANH</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>1039500.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>83160.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>1122660.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C26TKY</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3500410955</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>DOANH NGHIỆP TƯ NHÂN KIM YẾN</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê lợi, Phường Vũng Tàu , Thành Phố Hồ Chí Minh Việt Nam</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>8465460.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>846546.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>9312006.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C26TKY</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3500410955</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>DOANH NGHIỆP TƯ NHÂN KIM YẾN</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê lợi, Phường Vũng Tàu , Thành Phố Hồ Chí Minh Việt Nam</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>1.1521244E7</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>921700.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>1.2442944E7</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C26THM</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>49215</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3500442139</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>1127934.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>90235.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>143733.0</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>1218169.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C26THM</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>49384</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3500442139</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>2893288.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>231463.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>850786.0</v>
+      </c>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>3124751.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C26THM</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>49405</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3500442139</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>1104629.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>88370.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>1192999.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C26THM</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>49408</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3500442139</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>2328000.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>186240.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>2514240.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C26THM</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>49762</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3500442139</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>8844444.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>707556.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>9552000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C26THM</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>49763</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3500442139</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>2280909.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>182473.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>850786.0</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>2463382.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C26THM</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>49764</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3500442139</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>5681346.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>458599.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>2129867.0</v>
+      </c>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>6139945.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C26THM</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>50859</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3500442139</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH TÂM</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>2402400.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>192192.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>2594592.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C26TTT</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3500636705</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HOẠ MY</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>245A LÊ LỢI - PHƯỜNG VŨNG TÀU - THÀNH PHỐ HỒ CHÍ MINH - VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>1.11847273E8</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>1.1184727E7</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>1.23032E8</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C26TQT</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>6977</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3500678864</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ QUỐC THÁI</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>4658182.0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>465818.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>5124000.0</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C26TDH</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>17466</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3500788257</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu , TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>9777211.0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>782177.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>692069.0</v>
+      </c>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
+        <v>1.0559388E7</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C26TDH</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>17467</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3500788257</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu , TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>4721710.0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>377737.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>925230.0</v>
+      </c>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="n">
+        <v>5099447.0</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C26TDH</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>17586</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3500788257</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VÀ VẬN TẢI ĐÔNG HÒA PHÁT</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>2947236.0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>235779.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>138875.0</v>
+      </c>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="n">
+        <v>3183015.0</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C26TTH</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3500805921</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI HÙNG TRINH</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>1.8425926E7</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>1474074.0</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="n">
+        <v>1.99E7</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C26TAA</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3501783050</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>DOANH NGHIỆP TƯ NHÂN THƯƠNG MẠI SAO ANH</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>1.120032E7</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>896026.0</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="n">
+        <v>1.2096346E7</v>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C26TLH</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>40874</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3501970854</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>4435264.0</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>354821.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>44801.0</v>
+      </c>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13" t="n">
+        <v>4790085.0</v>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C26TLH</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>41040</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3501970854</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>6962963.0</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>557037.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="n">
+        <v>7520000.0</v>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C26TLH</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>41475</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3501970854</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>-1666667.0</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>-133333.0</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13" t="n">
+        <v>-1800000.0</v>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C26TLH</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>42887</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3501970854</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>1977279.0</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>197727.0</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>68181.0</v>
+      </c>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13" t="n">
+        <v>2175006.0</v>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C26TLH</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>42970</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3501970854</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n">
+        <v>1.3781389E7</v>
+      </c>
+      <c r="L38" s="13" t="n">
+        <v>1102511.0</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>394537.0</v>
+      </c>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13" t="n">
+        <v>1.48839E7</v>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C26TLH</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>44753</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3501970854</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HỮU LINH</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>3072960.0</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>245837.0</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>95040.0</v>
+      </c>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13" t="n">
+        <v>3318797.0</v>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C26THH</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3502203697</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI HIỀN HÙNG</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>Số 245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="n">
+        <v>1560185.0</v>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>124815.0</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13" t="n">
+        <v>1685000.0</v>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C26TPK</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>1642</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3502206560</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI PHƯƠNG KIM</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>Số 245 Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>1.9719546E7</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>1971954.0</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13" t="n">
+        <v>2.16915E7</v>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C26TPK</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>1643</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3502206560</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI PHƯƠNG KIM</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>Số 245 Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="n">
+        <v>1.1606944E7</v>
+      </c>
+      <c r="L42" s="13" t="n">
+        <v>928556.0</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>426388.0</v>
+      </c>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13" t="n">
+        <v>1.25355E7</v>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C26TPK</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>1697</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3502206560</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI PHƯƠNG KIM</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>Số 245 Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>4486364.0</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>448636.0</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13" t="n">
+        <v>4935000.0</v>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C26TPK</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>1698</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3502206560</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI PHƯƠNG KIM</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>Số 245 Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="n">
+        <v>3821296.0</v>
+      </c>
+      <c r="L44" s="13" t="n">
+        <v>305704.0</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13" t="n">
+        <v>4127000.0</v>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q44" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C26TTT</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>15621</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3502243033</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>4689815.0</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>375185.0</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N45" s="13"/>
+      <c r="O45" s="13" t="n">
+        <v>5065000.0</v>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C26TTT</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>15703</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3502243033</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI MINH GIA</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="n">
+        <v>1.3222222E7</v>
+      </c>
+      <c r="L46" s="13" t="n">
+        <v>1057778.0</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13" t="n">
+        <v>1.428E7</v>
+      </c>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q46" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>C26TVT</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>9571</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>3502252817</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>7.0752355E7</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>6601645.0</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13" t="n">
+        <v>7.7354E7</v>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>C26TVT</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>9572</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>3502252817</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="n">
+        <v>4.5323568E7</v>
+      </c>
+      <c r="L48" s="13" t="n">
+        <v>3960432.0</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13" t="n">
+        <v>4.9284E7</v>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q48" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>C26TVT</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>9573</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>3502252817</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ THƯƠNG MẠI DỊCH VỤ VIỆT TÍN THÀNH</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="n">
+        <v>1.9894192E7</v>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>1978808.0</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13" t="n">
+        <v>2.1873E7</v>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q49" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3502343006</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="n">
+        <v>2442963.0</v>
+      </c>
+      <c r="L50" s="13" t="n">
+        <v>229037.0</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13" t="n">
+        <v>2672000.0</v>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q50" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>1742</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3502343006</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="n">
+        <v>8527760.0</v>
+      </c>
+      <c r="L51" s="13" t="n">
+        <v>682221.0</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>1388320.0</v>
+      </c>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13" t="n">
+        <v>9209981.0</v>
+      </c>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q51" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>1743</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3502343006</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI MAI LINH PHÁT</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="n">
+        <v>1.6315683E7</v>
+      </c>
+      <c r="L52" s="13" t="n">
+        <v>1305255.0</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>2849316.0</v>
+      </c>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13" t="n">
+        <v>1.7620938E7</v>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q52" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C26TLP</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>2741</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3502376562</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THỰC PHẨM HƯNG LỘC PHÁT</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="n">
+        <v>2.0564815E7</v>
+      </c>
+      <c r="L53" s="13" t="n">
+        <v>1645185.0</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13" t="n">
+        <v>2.221E7</v>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q53" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C26TKN</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>5720</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3502380738</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH KIM NGỌC KHANG</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>245 A Lê Lợi , Phường Vũng Tàu , Thành Phố Hồ Chí Minh , Việt Nam</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="n">
+        <v>1.4727273E7</v>
+      </c>
+      <c r="L54" s="13" t="n">
+        <v>1472727.0</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13" t="n">
+        <v>1.62E7</v>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q54" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S54" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>C26TAU</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>2545</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="n">
+        <v>2875747.0</v>
+      </c>
+      <c r="L55" s="13" t="n">
+        <v>230060.0</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13" t="n">
+        <v>3105807.0</v>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S55" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>C26TMH</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>4819</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="n">
+        <v>1051635.0</v>
+      </c>
+      <c r="L56" s="13" t="n">
+        <v>84131.0</v>
+      </c>
+      <c r="M56" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13" t="n">
+        <v>1135766.0</v>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q56" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S56" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>C26TMH</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>3502426816</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THANH MẠNH HÙNG</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="n">
+        <v>5378062.0</v>
+      </c>
+      <c r="L57" s="13" t="n">
+        <v>430245.0</v>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13" t="n">
+        <v>5808307.0</v>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q57" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>C26TMQ</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>3502548074</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="n">
+        <v>3520000.0</v>
+      </c>
+      <c r="L58" s="13" t="n">
+        <v>281600.0</v>
+      </c>
+      <c r="M58" s="13"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13" t="n">
+        <v>3801600.0</v>
+      </c>
+      <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q58" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C26TMQ</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>3502548074</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH PHÂN PHỐI MINH VÀ QUÂN</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>5215800.0</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>417264.0</v>
+      </c>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13" t="n">
+        <v>5633064.0</v>
+      </c>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q59" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C26TDD</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>3502548116</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="n">
+        <v>3218519.0</v>
+      </c>
+      <c r="L60" s="13" t="n">
+        <v>257481.0</v>
+      </c>
+      <c r="M60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13" t="n">
+        <v>3476000.0</v>
+      </c>
+      <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q60" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S60" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C26TDD</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>3502548116</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐỨC DẬT</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="n">
+        <v>1.2583333E7</v>
+      </c>
+      <c r="L61" s="13" t="n">
+        <v>1006667.0</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13" t="n">
+        <v>1.359E7</v>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q61" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S61" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>12869</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>1.9582711E7</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>1566617.0</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13" t="n">
+        <v>2.1149328E7</v>
+      </c>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q62" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S62" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>12975</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>7474408.0</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>597952.0</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13" t="n">
+        <v>8072360.0</v>
+      </c>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q63" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S63" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>13191</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>327259.0</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>26181.0</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13" t="n">
+        <v>353440.0</v>
+      </c>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q64" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S64" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>13193</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>1.8582222E7</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>1486578.0</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N65" s="13"/>
+      <c r="O65" s="13" t="n">
+        <v>2.00688E7</v>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q65" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S65" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>13294</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>979285.0</v>
+      </c>
+      <c r="L66" s="13" t="n">
+        <v>78343.0</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>81920.0</v>
+      </c>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13" t="n">
+        <v>1057628.0</v>
+      </c>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q66" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S66" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>C26THP</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>13295</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="n">
+        <v>1735246.0</v>
+      </c>
+      <c r="L67" s="13" t="n">
+        <v>138821.0</v>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>35413.0</v>
+      </c>
+      <c r="N67" s="13"/>
+      <c r="O67" s="13" t="n">
+        <v>1874067.0</v>
+      </c>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q67" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S67" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>C26TDA</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>1938</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>3502563749</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ĐỨC ANH VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>245A Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="n">
+        <v>1.33587E8</v>
+      </c>
+      <c r="L68" s="13" t="n">
+        <v>1.33587E7</v>
+      </c>
+      <c r="M68" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N68" s="13"/>
+      <c r="O68" s="13" t="n">
+        <v>1.469457E8</v>
+      </c>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q68" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S68" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>C26TDM</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>3502580173</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DŨNG MUỐI</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245 A Lê Lợi , Phường Vũng Tàu , Thành Phố Hồ Chí Minh , Việt Nam </t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="n">
+        <v>1037037.0</v>
+      </c>
+      <c r="L69" s="13" t="n">
+        <v>82963.0</v>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N69" s="13"/>
+      <c r="O69" s="13" t="n">
+        <v>1120000.0</v>
+      </c>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q69" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>C26TBR</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>13578</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>3600244645-009</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY AJINOMOTO VIỆT NAM TẠI BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>245A LÊ LỢI, PHƯỜNG VŨNG TÀU, THÀNH PHỐ HỒ CHÍ MINH, VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="n">
+        <v>7885732.0</v>
+      </c>
+      <c r="L70" s="13" t="n">
+        <v>630859.0</v>
+      </c>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="13" t="n">
+        <v>8516591.0</v>
+      </c>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q70" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S70" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>
